--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q100_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01129657557679133</v>
+        <v>0.01005180277270287</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01129657557679133</v>
+        <v>0.01005180277270287</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02413296718856763</v>
+        <v>0.02193029339422874</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02413296718856763</v>
+        <v>0.02193029339422874</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04632681780383249</v>
+        <v>0.04186133814052695</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04632681780383249</v>
+        <v>0.04186133814052695</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06799617800870859</v>
+        <v>0.06160599678588105</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06799617800870859</v>
+        <v>0.06160599678588105</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0737507647302332</v>
+        <v>0.06677448574687898</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0737507647302332</v>
+        <v>0.06677448574687898</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06890664045913365</v>
+        <v>0.06237930391826892</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06890664045913365</v>
+        <v>0.06237930391826892</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06422612509156986</v>
+        <v>0.05815461009400061</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06422612509156986</v>
+        <v>0.05815461009400061</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0612308556763689</v>
+        <v>0.05554099609017437</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0612308556763689</v>
+        <v>0.05554099609017437</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
